--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>

--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>

--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>

--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -475,22 +475,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>198653</v>
+        <v>198688</v>
       </c>
       <c r="C2" t="n">
         <v>5.4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="E2" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3">
@@ -500,22 +500,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81098</v>
+        <v>80198</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2</v>
+        <v>-1.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>1384</v>
+        <v>1116</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -525,14 +525,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>159853</v>
+        <v>161184</v>
       </c>
       <c r="C4" t="n">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>1256</v>
+      </c>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -542,22 +544,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122149</v>
+        <v>122113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>1104</v>
+        <v>1125</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +569,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>163299</v>
+        <v>163957</v>
       </c>
       <c r="C6" t="n">
         <v>5.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>1011</v>
+        <v>977</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +594,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>205644</v>
+        <v>207962</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E7" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="F7" t="n">
-        <v>1244</v>
+        <v>1187</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="8">
@@ -617,22 +619,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>184615</v>
+        <v>185071</v>
       </c>
       <c r="C8" t="n">
         <v>3.6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1309</v>
+        <v>1273</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -642,7 +644,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98739</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -659,15 +661,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210999</v>
+        <v>213611</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>952</v>
+        <v>922</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -729,22 +731,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>741645</v>
+        <v>731562</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="D2" t="n">
-        <v>-18</v>
+        <v>-20.7</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="F2" t="n">
-        <v>3390</v>
+        <v>3488</v>
       </c>
       <c r="G2" t="n">
-        <v>13.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="3">
@@ -754,22 +756,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>812168</v>
+        <v>811986</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-24.9</v>
+        <v>-26.5</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="F3" t="n">
-        <v>4060</v>
+        <v>4085</v>
       </c>
       <c r="G3" t="n">
-        <v>18.7</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="4">
@@ -779,22 +781,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1103827</v>
+        <v>1095341</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-24</v>
+        <v>-25.9</v>
       </c>
       <c r="E4" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="F4" t="n">
-        <v>5289</v>
+        <v>5520</v>
       </c>
       <c r="G4" t="n">
-        <v>24.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="5">
@@ -804,22 +806,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1033061</v>
+        <v>1018312</v>
       </c>
       <c r="C5" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="D5" t="n">
-        <v>-25.1</v>
+        <v>-26</v>
       </c>
       <c r="E5" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="F5" t="n">
-        <v>4513</v>
+        <v>4647</v>
       </c>
       <c r="G5" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="6">
@@ -829,22 +831,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1035457</v>
+        <v>1028320</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>-15.6</v>
+        <v>-18.4</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>24.4</v>
       </c>
       <c r="F6" t="n">
-        <v>3315</v>
+        <v>3511</v>
       </c>
       <c r="G6" t="n">
-        <v>15.8</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="7">
@@ -854,22 +856,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1040528</v>
+        <v>1036077</v>
       </c>
       <c r="C7" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="D7" t="n">
-        <v>-19.2</v>
+        <v>-21.3</v>
       </c>
       <c r="E7" t="n">
-        <v>24.9</v>
+        <v>23.3</v>
       </c>
       <c r="F7" t="n">
-        <v>3483</v>
+        <v>3709</v>
       </c>
       <c r="G7" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -879,22 +881,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1386906</v>
+        <v>1390922</v>
       </c>
       <c r="C8" t="n">
-        <v>8.4</v>
+        <v>10.2</v>
       </c>
       <c r="D8" t="n">
-        <v>-13.1</v>
+        <v>-15.7</v>
       </c>
       <c r="E8" t="n">
-        <v>28</v>
+        <v>26.8</v>
       </c>
       <c r="F8" t="n">
-        <v>4127</v>
+        <v>4327</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="9">
@@ -904,22 +906,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1156683</v>
+        <v>1152963</v>
       </c>
       <c r="C9" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.6</v>
+        <v>-7.7</v>
       </c>
       <c r="E9" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="F9" t="n">
-        <v>3534</v>
+        <v>3389</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
@@ -929,22 +931,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1948470</v>
+        <v>1965149</v>
       </c>
       <c r="C10" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.1</v>
+        <v>-10</v>
       </c>
       <c r="E10" t="n">
-        <v>32.8</v>
+        <v>29.9</v>
       </c>
       <c r="F10" t="n">
-        <v>4952</v>
+        <v>5472</v>
       </c>
       <c r="G10" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="11">
@@ -954,22 +956,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1482150</v>
+        <v>1510670</v>
       </c>
       <c r="C11" t="n">
-        <v>9.9</v>
+        <v>12.2</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.2</v>
+        <v>-17.7</v>
       </c>
       <c r="E11" t="n">
-        <v>28.1</v>
+        <v>27.4</v>
       </c>
       <c r="F11" t="n">
-        <v>4394</v>
+        <v>4596</v>
       </c>
       <c r="G11" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="12">
@@ -979,22 +981,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1598620</v>
+        <v>1598935</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1</v>
+        <v>-5.6</v>
       </c>
       <c r="E12" t="n">
-        <v>39.8</v>
+        <v>36.6</v>
       </c>
       <c r="F12" t="n">
-        <v>3346</v>
+        <v>3597</v>
       </c>
       <c r="G12" t="n">
-        <v>9.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="13">
@@ -1004,22 +1006,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1616826</v>
+        <v>1642718</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.9</v>
+        <v>-16.4</v>
       </c>
       <c r="E13" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="F13" t="n">
-        <v>4232</v>
+        <v>4334</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="14">
@@ -1029,22 +1031,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2155271</v>
+        <v>2181808</v>
       </c>
       <c r="C14" t="n">
-        <v>9.300000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.4</v>
+        <v>-13.7</v>
       </c>
       <c r="E14" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="F14" t="n">
-        <v>4132</v>
+        <v>4212</v>
       </c>
       <c r="G14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1054,22 +1056,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1770873</v>
+        <v>1785975</v>
       </c>
       <c r="C15" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.5</v>
+        <v>-11.8</v>
       </c>
       <c r="E15" t="n">
-        <v>37.5</v>
+        <v>39.4</v>
       </c>
       <c r="F15" t="n">
-        <v>3938</v>
+        <v>3781</v>
       </c>
       <c r="G15" t="n">
-        <v>13.2</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="16">
@@ -1079,22 +1081,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1664037</v>
+        <v>1676343</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="D16" t="n">
-        <v>-9</v>
+        <v>-10.6</v>
       </c>
       <c r="E16" t="n">
-        <v>37.9</v>
+        <v>37.3</v>
       </c>
       <c r="F16" t="n">
-        <v>3656</v>
+        <v>3747</v>
       </c>
       <c r="G16" t="n">
-        <v>11.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="17">
@@ -1104,22 +1106,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2408450</v>
+        <v>2421080</v>
       </c>
       <c r="C17" t="n">
-        <v>11.5</v>
+        <v>13.7</v>
       </c>
       <c r="D17" t="n">
-        <v>-14.8</v>
+        <v>-15.7</v>
       </c>
       <c r="E17" t="n">
-        <v>43.7</v>
+        <v>41.5</v>
       </c>
       <c r="F17" t="n">
-        <v>4594</v>
+        <v>4858</v>
       </c>
       <c r="G17" t="n">
-        <v>24.5</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="18">
@@ -1129,15 +1131,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>929299</v>
+        <v>925651</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>4207</v>
+        <v>4093</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -1148,15 +1150,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1984558</v>
+        <v>1979625</v>
       </c>
       <c r="C19" t="n">
-        <v>10.1</v>
+        <v>12.6</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>5522</v>
+        <v>5527</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -1167,22 +1169,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1713078</v>
+        <v>1723951</v>
       </c>
       <c r="C20" t="n">
-        <v>11.2</v>
+        <v>13.5</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.9</v>
+        <v>-15.5</v>
       </c>
       <c r="E20" t="n">
-        <v>32.9</v>
+        <v>31.3</v>
       </c>
       <c r="F20" t="n">
-        <v>4337</v>
+        <v>4584</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="21">
@@ -1192,15 +1194,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1379412</v>
+        <v>1367238</v>
       </c>
       <c r="C21" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3289</v>
+        <v>3219</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -1211,22 +1213,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1369208</v>
+        <v>1381880</v>
       </c>
       <c r="C22" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.1</v>
+        <v>-15.8</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>4760</v>
+        <v>4598</v>
       </c>
       <c r="G22" t="n">
-        <v>20.1</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="23">
@@ -1236,15 +1238,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1084801</v>
+        <v>1072440</v>
       </c>
       <c r="C23" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>3937</v>
+        <v>4038</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -1255,22 +1257,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1320534</v>
+        <v>1343873</v>
       </c>
       <c r="C24" t="n">
-        <v>6.9</v>
+        <v>8.6</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.7</v>
+        <v>-23.8</v>
       </c>
       <c r="E24" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="F24" t="n">
-        <v>5207</v>
+        <v>5385</v>
       </c>
       <c r="G24" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1356,7 @@
         <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>141446</v>
+        <v>140970</v>
       </c>
       <c r="E2" t="n">
         <v>1770000</v>
@@ -1363,7 +1365,7 @@
         <v>-20085</v>
       </c>
       <c r="G2" t="n">
-        <v>836321</v>
+        <v>830235</v>
       </c>
       <c r="H2" t="n">
         <v>0.147</v>
@@ -1390,7 +1392,7 @@
         <v>40</v>
       </c>
       <c r="D3" t="n">
-        <v>60095</v>
+        <v>62224</v>
       </c>
       <c r="E3" t="n">
         <v>210000</v>
@@ -1399,7 +1401,7 @@
         <v>139</v>
       </c>
       <c r="G3" t="n">
-        <v>428748</v>
+        <v>428018</v>
       </c>
       <c r="H3" t="n">
         <v>0.172</v>
@@ -1445,7 +1447,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1471,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1495,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1507,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1519,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1543,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>

--- a/docs/exports/metrics_full.xlsx
+++ b/docs/exports/metrics_full.xlsx
@@ -475,22 +475,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>198688</v>
+        <v>197771</v>
       </c>
       <c r="C2" t="n">
         <v>5.4</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="E2" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1164</v>
+        <v>1145</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="3">
@@ -500,22 +500,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80198</v>
+        <v>80819</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.3</v>
+        <v>-3.7</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="F3" t="n">
-        <v>1116</v>
+        <v>1159</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4">
@@ -525,16 +525,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>161184</v>
+        <v>159186</v>
       </c>
       <c r="C4" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>1256</v>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -544,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122113</v>
+        <v>120910</v>
       </c>
       <c r="C5" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1125</v>
+        <v>1093</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -569,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>163957</v>
+        <v>162500</v>
       </c>
       <c r="C6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="F6" t="n">
-        <v>977</v>
+        <v>1000</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -594,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207962</v>
+        <v>207100</v>
       </c>
       <c r="C7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="F7" t="n">
-        <v>1187</v>
+        <v>1159</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="8">
@@ -619,22 +617,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>185071</v>
+        <v>183529</v>
       </c>
       <c r="C8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="F8" t="n">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -644,10 +642,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>98739</v>
+        <v>94087</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -661,15 +659,15 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213611</v>
+        <v>211379</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>922</v>
+        <v>991</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -731,22 +729,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>731562</v>
+        <v>745362</v>
       </c>
       <c r="C2" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="D2" t="n">
-        <v>-20.7</v>
+        <v>-22.9</v>
       </c>
       <c r="E2" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="F2" t="n">
-        <v>3488</v>
+        <v>3702</v>
       </c>
       <c r="G2" t="n">
-        <v>16.9</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="3">
@@ -756,22 +754,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>811986</v>
+        <v>823531</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="D3" t="n">
-        <v>-26.5</v>
+        <v>-29.1</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>4085</v>
+        <v>4287</v>
       </c>
       <c r="G3" t="n">
-        <v>21.1</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="4">
@@ -781,22 +779,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1095341</v>
+        <v>1127243</v>
       </c>
       <c r="C4" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.9</v>
+        <v>-26.8</v>
       </c>
       <c r="E4" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="F4" t="n">
-        <v>5520</v>
+        <v>5758</v>
       </c>
       <c r="G4" t="n">
-        <v>26.7</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="5">
@@ -806,22 +804,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1018312</v>
+        <v>1040849</v>
       </c>
       <c r="C5" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-26</v>
+        <v>-26.9</v>
       </c>
       <c r="E5" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="F5" t="n">
-        <v>4647</v>
+        <v>4781</v>
       </c>
       <c r="G5" t="n">
-        <v>23.8</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="6">
@@ -831,22 +829,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1028320</v>
+        <v>1045061</v>
       </c>
       <c r="C6" t="n">
-        <v>10.1</v>
+        <v>12.6</v>
       </c>
       <c r="D6" t="n">
-        <v>-18.4</v>
+        <v>-20.5</v>
       </c>
       <c r="E6" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="F6" t="n">
-        <v>3511</v>
+        <v>3677</v>
       </c>
       <c r="G6" t="n">
-        <v>20.5</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="7">
@@ -856,22 +854,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1036077</v>
+        <v>1065276</v>
       </c>
       <c r="C7" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-21.3</v>
+        <v>-23.1</v>
       </c>
       <c r="E7" t="n">
         <v>23.3</v>
       </c>
       <c r="F7" t="n">
-        <v>3709</v>
+        <v>3811</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="8">
@@ -881,22 +879,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1390922</v>
+        <v>1413716</v>
       </c>
       <c r="C8" t="n">
-        <v>10.2</v>
+        <v>12.6</v>
       </c>
       <c r="D8" t="n">
-        <v>-15.7</v>
+        <v>-17</v>
       </c>
       <c r="E8" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="F8" t="n">
-        <v>4327</v>
+        <v>4428</v>
       </c>
       <c r="G8" t="n">
-        <v>18.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="9">
@@ -906,22 +904,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1152963</v>
+        <v>1165294</v>
       </c>
       <c r="C9" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.7</v>
+        <v>-9.1</v>
       </c>
       <c r="E9" t="n">
-        <v>28.3</v>
+        <v>29.2</v>
       </c>
       <c r="F9" t="n">
-        <v>3389</v>
+        <v>3321</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10">
@@ -931,22 +929,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1965149</v>
+        <v>1997982</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>17.3</v>
       </c>
       <c r="D10" t="n">
-        <v>-10</v>
+        <v>-13.1</v>
       </c>
       <c r="E10" t="n">
-        <v>29.9</v>
+        <v>28.6</v>
       </c>
       <c r="F10" t="n">
-        <v>5472</v>
+        <v>5815</v>
       </c>
       <c r="G10" t="n">
-        <v>18.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="11">
@@ -956,22 +954,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1510670</v>
+        <v>1529903</v>
       </c>
       <c r="C11" t="n">
-        <v>12.2</v>
+        <v>14.7</v>
       </c>
       <c r="D11" t="n">
-        <v>-17.7</v>
+        <v>-18.9</v>
       </c>
       <c r="E11" t="n">
         <v>27.4</v>
       </c>
       <c r="F11" t="n">
-        <v>4596</v>
+        <v>4646</v>
       </c>
       <c r="G11" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="12">
@@ -981,22 +979,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1598935</v>
+        <v>1623833</v>
       </c>
       <c r="C12" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6</v>
+        <v>-12.8</v>
       </c>
       <c r="E12" t="n">
-        <v>36.6</v>
+        <v>31.5</v>
       </c>
       <c r="F12" t="n">
-        <v>3597</v>
+        <v>4299</v>
       </c>
       <c r="G12" t="n">
-        <v>10.9</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="13">
@@ -1006,22 +1004,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1642718</v>
+        <v>1668808</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>14.3</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.4</v>
+        <v>-18.3</v>
       </c>
       <c r="E13" t="n">
-        <v>31.6</v>
+        <v>29.1</v>
       </c>
       <c r="F13" t="n">
-        <v>4334</v>
+        <v>4779</v>
       </c>
       <c r="G13" t="n">
-        <v>22.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="14">
@@ -1031,22 +1029,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2181808</v>
+        <v>2240162</v>
       </c>
       <c r="C14" t="n">
-        <v>11.9</v>
+        <v>15.4</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.7</v>
+        <v>-12.2</v>
       </c>
       <c r="E14" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
       <c r="F14" t="n">
-        <v>4212</v>
+        <v>4247</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -1056,22 +1054,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1785975</v>
+        <v>1820717</v>
       </c>
       <c r="C15" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.8</v>
+        <v>-11.7</v>
       </c>
       <c r="E15" t="n">
-        <v>39.4</v>
+        <v>37.8</v>
       </c>
       <c r="F15" t="n">
-        <v>3781</v>
+        <v>4010</v>
       </c>
       <c r="G15" t="n">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="16">
@@ -1081,22 +1079,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1676343</v>
+        <v>1701483</v>
       </c>
       <c r="C16" t="n">
-        <v>8.9</v>
+        <v>11.4</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.6</v>
+        <v>-14.7</v>
       </c>
       <c r="E16" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>3747</v>
+        <v>3828</v>
       </c>
       <c r="G16" t="n">
-        <v>14.9</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="17">
@@ -1106,22 +1104,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2421080</v>
+        <v>2490120</v>
       </c>
       <c r="C17" t="n">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.7</v>
+        <v>-16.6</v>
       </c>
       <c r="E17" t="n">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="F17" t="n">
-        <v>4858</v>
+        <v>5052</v>
       </c>
       <c r="G17" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="18">
@@ -1131,15 +1129,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>925651</v>
+        <v>930768</v>
       </c>
       <c r="C18" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>4093</v>
+        <v>4013</v>
       </c>
       <c r="G18" t="inlineStr"/>
     </row>
@@ -1150,15 +1148,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1979625</v>
+        <v>2010403</v>
       </c>
       <c r="C19" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
-        <v>5527</v>
+        <v>5577</v>
       </c>
       <c r="G19" t="inlineStr"/>
     </row>
@@ -1169,22 +1167,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1723951</v>
+        <v>1747653</v>
       </c>
       <c r="C20" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
-        <v>-15.5</v>
+        <v>-18.4</v>
       </c>
       <c r="E20" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>4584</v>
+        <v>4551</v>
       </c>
       <c r="G20" t="n">
-        <v>20.7</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="21">
@@ -1194,15 +1192,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1367238</v>
+        <v>1373148</v>
       </c>
       <c r="C21" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>3219</v>
+        <v>3347</v>
       </c>
       <c r="G21" t="inlineStr"/>
     </row>
@@ -1213,22 +1211,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1381880</v>
+        <v>1420865</v>
       </c>
       <c r="C22" t="n">
-        <v>11.7</v>
+        <v>13.6</v>
       </c>
       <c r="D22" t="n">
-        <v>-15.8</v>
+        <v>-18.8</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
       <c r="F22" t="n">
-        <v>4598</v>
+        <v>4680</v>
       </c>
       <c r="G22" t="n">
-        <v>22.3</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="23">
@@ -1238,15 +1236,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1072440</v>
+        <v>1070089</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>4038</v>
+        <v>3870</v>
       </c>
       <c r="G23" t="inlineStr"/>
     </row>
@@ -1257,22 +1255,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1343873</v>
+        <v>1348043</v>
       </c>
       <c r="C24" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.8</v>
+        <v>-24</v>
       </c>
       <c r="E24" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="F24" t="n">
-        <v>5385</v>
+        <v>5587</v>
       </c>
       <c r="G24" t="n">
-        <v>25.6</v>
+        <v>27.1</v>
       </c>
     </row>
   </sheetData>
@@ -1471,7 +1469,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1505,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1517,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1529,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1541,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
